--- a/競輪場一覧.xlsx
+++ b/競輪場一覧.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\競輪AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD648DBE-2572-44E9-A7A9-B95633AC76D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161E82A2-1500-46D1-AABC-FAC17EF8EA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$43</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -316,7 +319,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -324,6 +327,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -333,29 +396,53 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -680,788 +767,789 @@
     <col min="2" max="2" width="11.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.75" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3">
-        <v>400</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="7">
+        <v>400</v>
+      </c>
+      <c r="E2" s="8">
         <v>51.3</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>30.6142</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
-        <v>400</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="10">
+        <v>400</v>
+      </c>
+      <c r="E3" s="11">
         <v>58.9</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="12">
         <v>32.251899999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="3">
-        <v>400</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="10">
+        <v>400</v>
+      </c>
+      <c r="E4" s="11">
         <v>62.7</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="12">
         <v>32.912500000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3">
-        <v>400</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="10">
+        <v>400</v>
+      </c>
+      <c r="E5" s="11">
         <v>63.1</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="12">
         <v>32.404699999999998</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="10">
         <v>335</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="11">
         <v>46.7</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="12">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3">
-        <v>400</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="10">
+        <v>400</v>
+      </c>
+      <c r="E7" s="11">
         <v>54.8</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="12">
         <v>31.506900000000002</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="10">
         <v>500</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="11">
         <v>63.3</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="12">
         <v>25.7956</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="10">
         <v>500</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="11">
         <v>66.7</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="12">
         <v>26.277799999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="3">
-        <v>400</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="10">
+        <v>400</v>
+      </c>
+      <c r="E10" s="11">
         <v>47.6</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="12">
         <v>29.4483</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3">
-        <v>400</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="10">
+        <v>400</v>
+      </c>
+      <c r="E11" s="11">
         <v>51.5</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="12">
         <v>32.176099999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="3">
-        <v>400</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="10">
+        <v>400</v>
+      </c>
+      <c r="E12" s="11">
         <v>58</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="12">
         <v>31.218299999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="10">
         <v>333</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="11">
         <v>38.200000000000003</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="12">
         <v>29.745000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="3">
-        <v>400</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="10">
+        <v>400</v>
+      </c>
+      <c r="E14" s="11">
         <v>58</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="12">
         <v>32.1706</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="3">
-        <v>400</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="10">
+        <v>400</v>
+      </c>
+      <c r="E15" s="11">
         <v>54.2</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="12">
         <v>31.476900000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="10">
         <v>333</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="11">
         <v>36.1</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="12">
         <v>35.57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="10">
         <v>333</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="11">
         <v>46.6</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="12">
         <v>34.6858</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="3">
-        <v>400</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="10">
+        <v>400</v>
+      </c>
+      <c r="E18" s="11">
         <v>56.4</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="12">
         <v>30.722799999999999</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3">
-        <v>400</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="10">
+        <v>400</v>
+      </c>
+      <c r="E19" s="11">
         <v>58.8</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="12">
         <v>34.029699999999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="3">
-        <v>400</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="10">
+        <v>400</v>
+      </c>
+      <c r="E20" s="11">
         <v>59.3</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="12">
         <v>32.251899999999999</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="3">
-        <v>400</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="D21" s="10">
+        <v>400</v>
+      </c>
+      <c r="E21" s="11">
         <v>56</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="12">
         <v>30.6189</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="3">
-        <v>400</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D22" s="10">
+        <v>400</v>
+      </c>
+      <c r="E22" s="11">
         <v>60.3</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="12">
         <v>33.839399999999998</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="10">
         <v>333</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="11">
         <v>43</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="12">
         <v>33.69</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="3">
-        <v>400</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D24" s="10">
+        <v>400</v>
+      </c>
+      <c r="E24" s="11">
         <v>61.5</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="12">
         <v>34.424700000000001</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="3">
-        <v>400</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D25" s="10">
+        <v>400</v>
+      </c>
+      <c r="E25" s="11">
         <v>62.4</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="12">
         <v>32.251899999999999</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="3">
-        <v>400</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D26" s="10">
+        <v>400</v>
+      </c>
+      <c r="E26" s="11">
         <v>52.8</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="12">
         <v>31.476900000000001</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="10">
         <v>333</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="11">
         <v>38</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="12">
         <v>33.429699999999997</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="3">
-        <v>400</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28" s="10">
+        <v>400</v>
+      </c>
+      <c r="E28" s="11">
         <v>47.3</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="12">
         <v>30.485299999999999</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="3">
-        <v>400</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="D29" s="10">
+        <v>400</v>
+      </c>
+      <c r="E29" s="11">
         <v>59.9</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="12">
         <v>32.251899999999999</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="3">
-        <v>400</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D30" s="10">
+        <v>400</v>
+      </c>
+      <c r="E30" s="11">
         <v>56.7</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="12">
         <v>30.933299999999999</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="3">
-        <v>400</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="D31" s="10">
+        <v>400</v>
+      </c>
+      <c r="E31" s="11">
         <v>47.9</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="12">
         <v>30.625800000000002</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="3">
-        <v>400</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="D32" s="10">
+        <v>400</v>
+      </c>
+      <c r="E32" s="11">
         <v>57.9</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="12">
         <v>32.527799999999999</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="10">
         <v>333</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="11">
         <v>42.5</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="12">
         <v>34.6858</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="3">
-        <v>400</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34" s="10">
+        <v>400</v>
+      </c>
+      <c r="E34" s="11">
         <v>54.8</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="12">
         <v>33.2639</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="3">
-        <v>400</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35" s="10">
+        <v>400</v>
+      </c>
+      <c r="E35" s="11">
         <v>55.5</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="12">
         <v>29.7742</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="10">
         <v>500</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="11">
         <v>52</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="12">
         <v>24.497499999999999</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="3">
-        <v>400</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37" s="10">
+        <v>400</v>
+      </c>
+      <c r="E37" s="11">
         <v>58.6</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="12">
         <v>34.03</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="3">
-        <v>400</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="D38" s="10">
+        <v>400</v>
+      </c>
+      <c r="E38" s="11">
         <v>56.9</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="12">
         <v>34.03</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="3">
-        <v>400</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="D39" s="10">
+        <v>400</v>
+      </c>
+      <c r="E39" s="11">
         <v>50.7</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="12">
         <v>31.476900000000001</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="3">
-        <v>400</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="D40" s="10">
+        <v>400</v>
+      </c>
+      <c r="E40" s="11">
         <v>64.400000000000006</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="12">
         <v>32.005299999999998</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="3">
-        <v>400</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41" s="10">
+        <v>400</v>
+      </c>
+      <c r="E41" s="11">
         <v>40.200000000000003</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="12">
         <v>31.476900000000001</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D42" s="3">
-        <v>400</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="D42" s="10">
+        <v>400</v>
+      </c>
+      <c r="E42" s="11">
         <v>59.9</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="12">
         <v>33.69</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D43" s="3">
-        <v>400</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43" s="13">
+        <v>400</v>
+      </c>
+      <c r="E43" s="14">
         <v>60.3</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="15">
         <v>34.258099999999999</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
